--- a/구성종목(PDF)TIME코스닥액티브_2026-03-24.xlsx
+++ b/구성종목(PDF)TIME코스닥액티브_2026-03-24.xlsx
@@ -15,141 +15,21 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="5">
   <si>
-    <t>일자</t>
+    <t>종목코드</t>
   </si>
   <si>
-    <t>기준가격(원)</t>
+    <t>종목명</t>
   </si>
   <si>
-    <t>시장가격(원)</t>
+    <t>수량</t>
   </si>
   <si>
-    <t>과표기준가(원)</t>
+    <t>평가금액(원)</t>
   </si>
   <si>
-    <t>등락률(%)</t>
-  </si>
-  <si>
-    <t>종가(원)</t>
-  </si>
-  <si>
-    <t>2026.03.23</t>
-  </si>
-  <si>
-    <t>11,159.51</t>
-  </si>
-  <si>
-    <t>11,160.00</t>
-  </si>
-  <si>
-    <t>11,747.67</t>
-  </si>
-  <si>
-    <t>2026.03.20</t>
-  </si>
-  <si>
-    <t>12,018.31</t>
-  </si>
-  <si>
-    <t>12,010.00</t>
-  </si>
-  <si>
-    <t>11,748.43</t>
-  </si>
-  <si>
-    <t>2026.03.19</t>
-  </si>
-  <si>
-    <t>11,851.47</t>
-  </si>
-  <si>
-    <t>11,885.00</t>
-  </si>
-  <si>
-    <t>11,748.69</t>
-  </si>
-  <si>
-    <t>2026.03.18</t>
-  </si>
-  <si>
-    <t>12,016.25</t>
-  </si>
-  <si>
-    <t>12,040.00</t>
-  </si>
-  <si>
-    <t>11,748.93</t>
-  </si>
-  <si>
-    <t>2026.03.17</t>
-  </si>
-  <si>
-    <t>11,676.15</t>
-  </si>
-  <si>
-    <t>11,685.00</t>
-  </si>
-  <si>
-    <t>11,749.18</t>
-  </si>
-  <si>
-    <t>2026.03.16</t>
-  </si>
-  <si>
-    <t>11,895.81</t>
-  </si>
-  <si>
-    <t>11,925.00</t>
-  </si>
-  <si>
-    <t>11,749.43</t>
-  </si>
-  <si>
-    <t>2026.03.13</t>
-  </si>
-  <si>
-    <t>12,161.22</t>
-  </si>
-  <si>
-    <t>12,170.00</t>
-  </si>
-  <si>
-    <t>11,750.21</t>
-  </si>
-  <si>
-    <t>2026.03.12</t>
-  </si>
-  <si>
-    <t>12,128.39</t>
-  </si>
-  <si>
-    <t>12,160.00</t>
-  </si>
-  <si>
-    <t>11,750.48</t>
-  </si>
-  <si>
-    <t>2026.03.11</t>
-  </si>
-  <si>
-    <t>11,974.15</t>
-  </si>
-  <si>
-    <t>11,750.52</t>
-  </si>
-  <si>
-    <t>2026.03.10</t>
-  </si>
-  <si>
-    <t>12,189.20</t>
-  </si>
-  <si>
-    <t>12,240.00</t>
-  </si>
-  <si>
-    <t>11,750.79</t>
+    <t>비중(%)</t>
   </si>
 </sst>
 </file>
@@ -218,12 +98,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
   </cellXfs>
@@ -525,7 +402,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="true" style="0"/>
@@ -533,248 +410,26 @@
     <col min="3" max="3" width="30" customWidth="true" style="0"/>
     <col min="4" max="4" width="30" customWidth="true" style="0"/>
     <col min="5" max="5" width="30" customWidth="true" style="0"/>
-    <col min="6" max="6" width="30" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" customHeight="1" ht="33">
+    <row r="1" spans="1:5" customHeight="1" ht="33">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" customHeight="1" ht="33">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" s="1"/>
-    </row>
-    <row r="3" spans="1:6" customHeight="1" ht="30">
-      <c r="A3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="2">
-        <v>-7.15</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="2">
-        <v>-7.08</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" customHeight="1" ht="30">
-      <c r="A4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="2">
-        <v>1.41</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="2">
-        <v>1.05</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" customHeight="1" ht="30">
-      <c r="A5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="2">
-        <v>-1.37</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" s="2">
-        <v>-1.29</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" customHeight="1" ht="30">
-      <c r="A6" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="2">
-        <v>2.91</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" s="2">
-        <v>3.04</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" customHeight="1" ht="30">
-      <c r="A7" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" s="2">
-        <v>-1.85</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E7" s="2">
-        <v>-2.01</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" customHeight="1" ht="30">
-      <c r="A8" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="2">
-        <v>-2.18</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E8" s="2">
-        <v>-2.01</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" customHeight="1" ht="30">
-      <c r="A9" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" s="2">
-        <v>0.27</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E9" s="2">
-        <v>0.08</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" customHeight="1" ht="30">
-      <c r="A10" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C10" s="2">
-        <v>1.29</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E10" s="2">
-        <v>1.25</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" customHeight="1" ht="30">
-      <c r="A11" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C11" s="2">
-        <v>-1.76</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E11" s="2">
-        <v>-1.88</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" customHeight="1" ht="30">
-      <c r="A12" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C12" s="2">
-        <v>3.73</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E12" s="2">
-        <v>4.13</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>44</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="F1:F2"/>
-  </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/구성종목(PDF)TIME코스닥액티브_2026-03-24.xlsx
+++ b/구성종목(PDF)TIME코스닥액티브_2026-03-24.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="150">
   <si>
     <t>종목코드</t>
   </si>
@@ -30,6 +30,441 @@
   </si>
   <si>
     <t>비중(%)</t>
+  </si>
+  <si>
+    <t>000250</t>
+  </si>
+  <si>
+    <t>삼천당제약</t>
+  </si>
+  <si>
+    <t>44,928,000</t>
+  </si>
+  <si>
+    <t>에이비엘바이오</t>
+  </si>
+  <si>
+    <t>34,580,000</t>
+  </si>
+  <si>
+    <t>086520</t>
+  </si>
+  <si>
+    <t>에코프로</t>
+  </si>
+  <si>
+    <t>21,605,000</t>
+  </si>
+  <si>
+    <t>알지노믹스</t>
+  </si>
+  <si>
+    <t>20,850,000</t>
+  </si>
+  <si>
+    <t>로보티즈</t>
+  </si>
+  <si>
+    <t>20,720,000</t>
+  </si>
+  <si>
+    <t>리가켐바이오</t>
+  </si>
+  <si>
+    <t>19,992,000</t>
+  </si>
+  <si>
+    <t>리브스메드</t>
+  </si>
+  <si>
+    <t>16,769,600</t>
+  </si>
+  <si>
+    <t>095340</t>
+  </si>
+  <si>
+    <t>ISC</t>
+  </si>
+  <si>
+    <t>16,456,500</t>
+  </si>
+  <si>
+    <t>파두</t>
+  </si>
+  <si>
+    <t>16,300,800</t>
+  </si>
+  <si>
+    <t>아이티센글로벌</t>
+  </si>
+  <si>
+    <t>14,622,800</t>
+  </si>
+  <si>
+    <t>오름테라퓨틱</t>
+  </si>
+  <si>
+    <t>13,493,200</t>
+  </si>
+  <si>
+    <t>에스티팜</t>
+  </si>
+  <si>
+    <t>12,080,000</t>
+  </si>
+  <si>
+    <t>089970</t>
+  </si>
+  <si>
+    <t>브이엠</t>
+  </si>
+  <si>
+    <t>11,737,500</t>
+  </si>
+  <si>
+    <t>원익IPS</t>
+  </si>
+  <si>
+    <t>11,718,900</t>
+  </si>
+  <si>
+    <t>0009K0</t>
+  </si>
+  <si>
+    <t>에임드바이오</t>
+  </si>
+  <si>
+    <t>11,700,000</t>
+  </si>
+  <si>
+    <t>099320</t>
+  </si>
+  <si>
+    <t>쎄트렉아이</t>
+  </si>
+  <si>
+    <t>11,463,800</t>
+  </si>
+  <si>
+    <t>올릭스</t>
+  </si>
+  <si>
+    <t>11,058,000</t>
+  </si>
+  <si>
+    <t>알테오젠</t>
+  </si>
+  <si>
+    <t>11,020,500</t>
+  </si>
+  <si>
+    <t>039030</t>
+  </si>
+  <si>
+    <t>이오테크닉스</t>
+  </si>
+  <si>
+    <t>11,011,000</t>
+  </si>
+  <si>
+    <t>058470</t>
+  </si>
+  <si>
+    <t>리노공업</t>
+  </si>
+  <si>
+    <t>10,730,000</t>
+  </si>
+  <si>
+    <t>기가비스</t>
+  </si>
+  <si>
+    <t>10,500,000</t>
+  </si>
+  <si>
+    <t>083650</t>
+  </si>
+  <si>
+    <t>비에이치아이</t>
+  </si>
+  <si>
+    <t>10,217,600</t>
+  </si>
+  <si>
+    <t>현금</t>
+  </si>
+  <si>
+    <t>9,698,781</t>
+  </si>
+  <si>
+    <t>한국피아이엠</t>
+  </si>
+  <si>
+    <t>9,345,000</t>
+  </si>
+  <si>
+    <t>036930</t>
+  </si>
+  <si>
+    <t>주성엔지니어링</t>
+  </si>
+  <si>
+    <t>9,133,200</t>
+  </si>
+  <si>
+    <t>067310</t>
+  </si>
+  <si>
+    <t>하나마이크론</t>
+  </si>
+  <si>
+    <t>8,162,500</t>
+  </si>
+  <si>
+    <t>084370</t>
+  </si>
+  <si>
+    <t>유진테크</t>
+  </si>
+  <si>
+    <t>7,967,000</t>
+  </si>
+  <si>
+    <t>058610</t>
+  </si>
+  <si>
+    <t>에스피지</t>
+  </si>
+  <si>
+    <t>7,852,200</t>
+  </si>
+  <si>
+    <t>RF머트리얼즈</t>
+  </si>
+  <si>
+    <t>6,882,000</t>
+  </si>
+  <si>
+    <t>LS머트리얼즈</t>
+  </si>
+  <si>
+    <t>6,552,000</t>
+  </si>
+  <si>
+    <t>RFHIC</t>
+  </si>
+  <si>
+    <t>6,494,000</t>
+  </si>
+  <si>
+    <t>032820</t>
+  </si>
+  <si>
+    <t>우리기술</t>
+  </si>
+  <si>
+    <t>6,410,850</t>
+  </si>
+  <si>
+    <t>에이치브이엠</t>
+  </si>
+  <si>
+    <t>6,258,000</t>
+  </si>
+  <si>
+    <t>한중엔시에스</t>
+  </si>
+  <si>
+    <t>6,192,000</t>
+  </si>
+  <si>
+    <t>레인보우로보틱스</t>
+  </si>
+  <si>
+    <t>6,020,000</t>
+  </si>
+  <si>
+    <t>지투지바이오</t>
+  </si>
+  <si>
+    <t>5,945,000</t>
+  </si>
+  <si>
+    <t>노타</t>
+  </si>
+  <si>
+    <t>5,916,750</t>
+  </si>
+  <si>
+    <t>디앤디파마텍</t>
+  </si>
+  <si>
+    <t>5,896,000</t>
+  </si>
+  <si>
+    <t>씨어스테크놀로지</t>
+  </si>
+  <si>
+    <t>5,460,000</t>
+  </si>
+  <si>
+    <t>솔브레인</t>
+  </si>
+  <si>
+    <t>5,124,000</t>
+  </si>
+  <si>
+    <t>보로노이</t>
+  </si>
+  <si>
+    <t>4,904,000</t>
+  </si>
+  <si>
+    <t>케어젠</t>
+  </si>
+  <si>
+    <t>4,725,000</t>
+  </si>
+  <si>
+    <t>실리콘투</t>
+  </si>
+  <si>
+    <t>4,680,000</t>
+  </si>
+  <si>
+    <t>064760</t>
+  </si>
+  <si>
+    <t>티씨케이</t>
+  </si>
+  <si>
+    <t>4,600,000</t>
+  </si>
+  <si>
+    <t>파인엠텍</t>
+  </si>
+  <si>
+    <t>4,515,400</t>
+  </si>
+  <si>
+    <t>039200</t>
+  </si>
+  <si>
+    <t>오스코텍</t>
+  </si>
+  <si>
+    <t>4,244,400</t>
+  </si>
+  <si>
+    <t>두산테스나</t>
+  </si>
+  <si>
+    <t>4,168,000</t>
+  </si>
+  <si>
+    <t>디케이티</t>
+  </si>
+  <si>
+    <t>3,999,900</t>
+  </si>
+  <si>
+    <t>레이크머티리얼즈</t>
+  </si>
+  <si>
+    <t>3,948,300</t>
+  </si>
+  <si>
+    <t>덕산네오룩스</t>
+  </si>
+  <si>
+    <t>3,751,800</t>
+  </si>
+  <si>
+    <t>프로티나</t>
+  </si>
+  <si>
+    <t>3,610,000</t>
+  </si>
+  <si>
+    <t>060370</t>
+  </si>
+  <si>
+    <t>LS마린솔루션</t>
+  </si>
+  <si>
+    <t>3,593,800</t>
+  </si>
+  <si>
+    <t>네오셈</t>
+  </si>
+  <si>
+    <t>3,455,380</t>
+  </si>
+  <si>
+    <t>피에스케이</t>
+  </si>
+  <si>
+    <t>3,112,200</t>
+  </si>
+  <si>
+    <t>앱클론</t>
+  </si>
+  <si>
+    <t>3,105,000</t>
+  </si>
+  <si>
+    <t>HPSP</t>
+  </si>
+  <si>
+    <t>3,071,250</t>
+  </si>
+  <si>
+    <t>098070</t>
+  </si>
+  <si>
+    <t>한텍</t>
+  </si>
+  <si>
+    <t>3,032,400</t>
+  </si>
+  <si>
+    <t>아이티켐</t>
+  </si>
+  <si>
+    <t>2,875,200</t>
+  </si>
+  <si>
+    <t>044490</t>
+  </si>
+  <si>
+    <t>태웅</t>
+  </si>
+  <si>
+    <t>2,538,700</t>
+  </si>
+  <si>
+    <t>서진시스템</t>
+  </si>
+  <si>
+    <t>2,460,000</t>
+  </si>
+  <si>
+    <t>알멕</t>
+  </si>
+  <si>
+    <t>2,441,600</t>
+  </si>
+  <si>
+    <t>와이지엔터테인먼트</t>
+  </si>
+  <si>
+    <t>2,160,600</t>
+  </si>
+  <si>
+    <t>선익시스템</t>
+  </si>
+  <si>
+    <t>2,050,400</t>
   </si>
 </sst>
 </file>
@@ -98,9 +533,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
   </cellXfs>
@@ -402,7 +840,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E64"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="true" style="0"/>
@@ -429,6 +867,1075 @@
         <v>4</v>
       </c>
     </row>
+    <row r="2" spans="1:5" customHeight="1" ht="30">
+      <c r="A2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="2">
+        <v>48</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="2">
+        <v>7.88</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" customHeight="1" ht="30">
+      <c r="A3" s="2">
+        <v>298380</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="2">
+        <v>200</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="2">
+        <v>6.07</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" customHeight="1" ht="30">
+      <c r="A4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="2">
+        <v>145</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="2">
+        <v>3.79</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" customHeight="1" ht="30">
+      <c r="A5" s="2">
+        <v>476830</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="2">
+        <v>100</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="2">
+        <v>3.66</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" customHeight="1" ht="30">
+      <c r="A6" s="2">
+        <v>108490</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="2">
+        <v>80</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="2">
+        <v>3.64</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" customHeight="1" ht="30">
+      <c r="A7" s="2">
+        <v>141080</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="2">
+        <v>98</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="2">
+        <v>3.51</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" customHeight="1" ht="30">
+      <c r="A8" s="2">
+        <v>491000</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="2">
+        <v>223</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="2">
+        <v>2.94</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" customHeight="1" ht="30">
+      <c r="A9" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="2">
+        <v>69</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="2">
+        <v>2.89</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" customHeight="1" ht="30">
+      <c r="A10" s="2">
+        <v>440110</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="2">
+        <v>288</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" s="2">
+        <v>2.86</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" customHeight="1" ht="30">
+      <c r="A11" s="2">
+        <v>124500</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="2">
+        <v>263</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E11" s="2">
+        <v>2.57</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" customHeight="1" ht="30">
+      <c r="A12" s="2">
+        <v>475830</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" s="2">
+        <v>122</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E12" s="2">
+        <v>2.37</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" customHeight="1" ht="30">
+      <c r="A13" s="2">
+        <v>237690</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="2">
+        <v>80</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E13" s="2">
+        <v>2.12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" customHeight="1" ht="30">
+      <c r="A14" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" s="2">
+        <v>250</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E14" s="2">
+        <v>2.06</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" customHeight="1" ht="30">
+      <c r="A15" s="2">
+        <v>240810</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" s="2">
+        <v>87</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E15" s="2">
+        <v>2.06</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" customHeight="1" ht="30">
+      <c r="A16" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" s="2">
+        <v>234</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E16" s="2">
+        <v>2.05</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" customHeight="1" ht="30">
+      <c r="A17" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C17" s="2">
+        <v>62</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E17" s="2">
+        <v>2.01</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" customHeight="1" ht="30">
+      <c r="A18" s="2">
+        <v>226950</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C18" s="2">
+        <v>60</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E18" s="2">
+        <v>1.94</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" customHeight="1" ht="30">
+      <c r="A19" s="2">
+        <v>196170</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C19" s="2">
+        <v>31</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E19" s="2">
+        <v>1.93</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" customHeight="1" ht="30">
+      <c r="A20" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C20" s="2">
+        <v>26</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E20" s="2">
+        <v>1.93</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" customHeight="1" ht="30">
+      <c r="A21" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C21" s="2">
+        <v>100</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E21" s="2">
+        <v>1.88</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" customHeight="1" ht="30">
+      <c r="A22" s="2">
+        <v>420770</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C22" s="2">
+        <v>150</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E22" s="2">
+        <v>1.84</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" customHeight="1" ht="30">
+      <c r="A23" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C23" s="2">
+        <v>103</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E23" s="2">
+        <v>1.79</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" customHeight="1" ht="30">
+      <c r="A24" s="2"/>
+      <c r="B24" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E24" s="2">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" customHeight="1" ht="30">
+      <c r="A25" s="2">
+        <v>448900</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C25" s="2">
+        <v>89</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E25" s="2">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" customHeight="1" ht="30">
+      <c r="A26" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C26" s="2">
+        <v>118</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E26" s="2">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" customHeight="1" ht="30">
+      <c r="A27" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C27" s="2">
+        <v>250</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E27" s="2">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" customHeight="1" ht="30">
+      <c r="A28" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C28" s="2">
+        <v>62</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E28" s="2">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" customHeight="1" ht="30">
+      <c r="A29" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C29" s="2">
+        <v>69</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E29" s="2">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" customHeight="1" ht="30">
+      <c r="A30" s="2">
+        <v>327260</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C30" s="2">
+        <v>111</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E30" s="2">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" customHeight="1" ht="30">
+      <c r="A31" s="2">
+        <v>417200</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C31" s="2">
+        <v>312</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E31" s="2">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" customHeight="1" ht="30">
+      <c r="A32" s="2">
+        <v>218410</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C32" s="2">
+        <v>85</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E32" s="2">
+        <v>1.14</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" customHeight="1" ht="30">
+      <c r="A33" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C33" s="2">
+        <v>237</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E33" s="2">
+        <v>1.13</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" customHeight="1" ht="30">
+      <c r="A34" s="2">
+        <v>295310</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C34" s="2">
+        <v>60</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E34" s="2">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" customHeight="1" ht="30">
+      <c r="A35" s="2">
+        <v>107640</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C35" s="2">
+        <v>120</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E35" s="2">
+        <v>1.09</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" customHeight="1" ht="30">
+      <c r="A36" s="2">
+        <v>277810</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C36" s="2">
+        <v>10</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E36" s="2">
+        <v>1.06</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" customHeight="1" ht="30">
+      <c r="A37" s="2">
+        <v>456160</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C37" s="2">
+        <v>82</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E37" s="2">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" customHeight="1" ht="30">
+      <c r="A38" s="2">
+        <v>486990</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C38" s="2">
+        <v>147</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E38" s="2">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" customHeight="1" ht="30">
+      <c r="A39" s="2">
+        <v>347850</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C39" s="2">
+        <v>80</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E39" s="2">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" customHeight="1" ht="30">
+      <c r="A40" s="2">
+        <v>458870</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C40" s="2">
+        <v>100</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E40" s="2">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" customHeight="1" ht="30">
+      <c r="A41" s="2">
+        <v>357780</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C41" s="2">
+        <v>12</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E41" s="2">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" customHeight="1" ht="30">
+      <c r="A42" s="2">
+        <v>310210</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C42" s="2">
+        <v>16</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E42" s="2">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" customHeight="1" ht="30">
+      <c r="A43" s="2">
+        <v>214370</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C43" s="2">
+        <v>45</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E43" s="2">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" customHeight="1" ht="30">
+      <c r="A44" s="2">
+        <v>257720</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C44" s="2">
+        <v>120</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E44" s="2">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" customHeight="1" ht="30">
+      <c r="A45" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C45" s="2">
+        <v>20</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E45" s="2">
+        <v>0.81</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" customHeight="1" ht="30">
+      <c r="A46" s="2">
+        <v>441270</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C46" s="2">
+        <v>422</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E46" s="2">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" customHeight="1" ht="30">
+      <c r="A47" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C47" s="2">
+        <v>81</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E47" s="2">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" customHeight="1" ht="30">
+      <c r="A48" s="2">
+        <v>131970</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C48" s="2">
+        <v>40</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E48" s="2">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" customHeight="1" ht="30">
+      <c r="A49" s="2">
+        <v>290550</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C49" s="2">
+        <v>201</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="E49" s="2">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" customHeight="1" ht="30">
+      <c r="A50" s="2">
+        <v>281740</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C50" s="2">
+        <v>205</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E50" s="2">
+        <v>0.69</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" customHeight="1" ht="30">
+      <c r="A51" s="2">
+        <v>213420</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C51" s="2">
+        <v>78</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E51" s="2">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" customHeight="1" ht="30">
+      <c r="A52" s="2">
+        <v>468530</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C52" s="2">
+        <v>50</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="E52" s="2">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" customHeight="1" ht="30">
+      <c r="A53" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C53" s="2">
+        <v>119</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="E53" s="2">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" customHeight="1" ht="30">
+      <c r="A54" s="2">
+        <v>253590</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C54" s="2">
+        <v>197</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="E54" s="2">
+        <v>0.61</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" customHeight="1" ht="30">
+      <c r="A55" s="2">
+        <v>319660</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C55" s="2">
+        <v>39</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E55" s="2">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" customHeight="1" ht="30">
+      <c r="A56" s="2">
+        <v>174900</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C56" s="2">
+        <v>46</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="E56" s="2">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" customHeight="1" ht="30">
+      <c r="A57" s="2">
+        <v>403870</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C57" s="2">
+        <v>63</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E57" s="2">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" customHeight="1" ht="30">
+      <c r="A58" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C58" s="2">
+        <v>57</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E58" s="2">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" customHeight="1" ht="30">
+      <c r="A59" s="2">
+        <v>309710</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C59" s="2">
+        <v>96</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="E59" s="2">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" customHeight="1" ht="30">
+      <c r="A60" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C60" s="2">
+        <v>53</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="E60" s="2">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" customHeight="1" ht="30">
+      <c r="A61" s="2">
+        <v>178320</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C61" s="2">
+        <v>50</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E61" s="2">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" customHeight="1" ht="30">
+      <c r="A62" s="2">
+        <v>354320</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C62" s="2">
+        <v>56</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E62" s="2">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" customHeight="1" ht="30">
+      <c r="A63" s="2">
+        <v>122870</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C63" s="2">
+        <v>39</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="E63" s="2">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" customHeight="1" ht="30">
+      <c r="A64" s="2">
+        <v>171090</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C64" s="2">
+        <v>22</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E64" s="2">
+        <v>0.36</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
